--- a/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
+++ b/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1398,17 +1390,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1492,17 +1476,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1586,17 +1562,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1680,17 +1648,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1774,17 +1734,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1868,17 +1820,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1962,17 +1906,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2056,17 +1992,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2150,17 +2078,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2244,17 +2164,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2338,17 +2250,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2432,17 +2336,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2526,17 +2422,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2620,17 +2508,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2714,17 +2594,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2807,16 +2679,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2867,16 +2731,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2927,16 +2783,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2987,16 +2835,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3047,16 +2887,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3107,16 +2939,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3167,16 +2991,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3227,16 +3043,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2204A01</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2204001</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
+++ b/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2204A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22041</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H암보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
+++ b/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>2204001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
+++ b/output/upload/S00026_2204_시그니처H암보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
